--- a/InputData/elec/ESTRTE/Elec Storage Tech Round Trip Efficiency.xlsx
+++ b/InputData/elec/ESTRTE/Elec Storage Tech Round Trip Efficiency.xlsx
@@ -1,54 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\ESTRTE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\elec\GBRTE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D7AA2D-10BF-408D-934D-9999807D83BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0810523-4B82-4275-B69B-DF6216DAAA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11775" yWindow="945" windowWidth="34050" windowHeight="22035" xr2:uid="{F5DFE386-DBEF-4AF1-963C-2CAABB7180AC}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="ESTRTE-grid-batteries" sheetId="2" r:id="rId2"/>
     <sheet name="ESTRTE-pumped-hydro" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>U.S. Energy Information Administration</t>
+  </si>
+  <si>
+    <t>Utility-scale batteries and pumped storage return about 80% of the electricity they store</t>
+  </si>
+  <si>
+    <t>https://www.eia.gov/todayinenergy/detail.php?id=46756</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (% of stored electricity returned)</t>
+  </si>
+  <si>
+    <t>Round-trip efficiency</t>
+  </si>
+  <si>
+    <t>Grid batteries</t>
+  </si>
   <si>
     <t>ESTRTE Electricity Storage Technology Round-Trip Efficiency</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>U.S. Energy Information Administration</t>
-  </si>
-  <si>
-    <t>Utility-scale batteries and pumped storage return about 80% of the electricity they store</t>
-  </si>
-  <si>
-    <t>https://www.eia.gov/todayinenergy/detail.php?id=46756</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (% of stored electricity returned)</t>
-  </si>
-  <si>
-    <t>Grid batteries</t>
-  </si>
-  <si>
-    <t>Round-trip efficiency</t>
   </si>
   <si>
     <t>Pumped hydro</t>
@@ -110,7 +123,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -436,24 +449,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14EBD16E-FF3E-46B9-95CB-C7A74EFA7439}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -463,25 +473,25 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{89ED04FB-7AC1-4722-B30E-71BDE7025CA9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9FA380-0802-4E12-9AD5-66B7BCF215AB}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -492,17 +502,17 @@
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0.82</v>
@@ -514,7 +524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB52EC4-0D58-482D-95ED-6F4A6D21B80A}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -525,17 +535,17 @@
     <col min="2" max="2" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>0.79</v>
